--- a/artfynd/A 3942-2025 artfynd.xlsx
+++ b/artfynd/A 3942-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122837222</v>
+        <v>122837223</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>90909</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570597</v>
+        <v>570628</v>
       </c>
       <c r="R2" t="n">
-        <v>6685181</v>
+        <v>6685316</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122837236</v>
+        <v>122837222</v>
       </c>
       <c r="B3" t="n">
-        <v>92221</v>
+        <v>5193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570595</v>
+        <v>570597</v>
       </c>
       <c r="R3" t="n">
-        <v>6685327</v>
+        <v>6685181</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122837225</v>
+        <v>122837236</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>92225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,43 +896,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570644</v>
+        <v>570595</v>
       </c>
       <c r="R4" t="n">
-        <v>6685226</v>
+        <v>6685327</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837226</v>
+        <v>122837225</v>
       </c>
       <c r="B5" t="n">
         <v>57494</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570647</v>
+        <v>570644</v>
       </c>
       <c r="R5" t="n">
-        <v>6684973</v>
+        <v>6685226</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1096,7 @@
         <v>122837234</v>
       </c>
       <c r="B6" t="n">
-        <v>80719</v>
+        <v>80723</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122837223</v>
+        <v>122837226</v>
       </c>
       <c r="B7" t="n">
-        <v>90905</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,38 +1207,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570628</v>
+        <v>570647</v>
       </c>
       <c r="R7" t="n">
-        <v>6685316</v>
+        <v>6684973</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 3942-2025 artfynd.xlsx
+++ b/artfynd/A 3942-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122837222</v>
+        <v>122837225</v>
       </c>
       <c r="B3" t="n">
-        <v>5193</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,20 +789,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -813,7 +813,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570597</v>
+        <v>570644</v>
       </c>
       <c r="R3" t="n">
-        <v>6685181</v>
+        <v>6685226</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122837236</v>
+        <v>122837234</v>
       </c>
       <c r="B4" t="n">
-        <v>92225</v>
+        <v>80723</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570595</v>
+        <v>570628</v>
       </c>
       <c r="R4" t="n">
-        <v>6685327</v>
+        <v>6685273</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837225</v>
+        <v>122837236</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>92225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,43 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570644</v>
+        <v>570595</v>
       </c>
       <c r="R5" t="n">
-        <v>6685226</v>
+        <v>6685327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122837234</v>
+        <v>122837222</v>
       </c>
       <c r="B6" t="n">
-        <v>80723</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,38 +1100,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1049</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570628</v>
+        <v>570597</v>
       </c>
       <c r="R6" t="n">
-        <v>6685273</v>
+        <v>6685181</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 3942-2025 artfynd.xlsx
+++ b/artfynd/A 3942-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122837223</v>
+        <v>122837226</v>
       </c>
       <c r="B2" t="n">
-        <v>90909</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570628</v>
+        <v>570647</v>
       </c>
       <c r="R2" t="n">
-        <v>6685316</v>
+        <v>6684973</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122837234</v>
+        <v>122837222</v>
       </c>
       <c r="B4" t="n">
-        <v>80723</v>
+        <v>5193</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,38 +901,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570628</v>
+        <v>570597</v>
       </c>
       <c r="R4" t="n">
-        <v>6685273</v>
+        <v>6685181</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837236</v>
+        <v>122837223</v>
       </c>
       <c r="B5" t="n">
-        <v>92225</v>
+        <v>90909</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570595</v>
+        <v>570628</v>
       </c>
       <c r="R5" t="n">
-        <v>6685327</v>
+        <v>6685316</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122837222</v>
+        <v>122837234</v>
       </c>
       <c r="B6" t="n">
-        <v>5193</v>
+        <v>80723</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,43 +1110,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>1049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570597</v>
+        <v>570628</v>
       </c>
       <c r="R6" t="n">
-        <v>6685181</v>
+        <v>6685273</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122837226</v>
+        <v>122837236</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>92225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,43 +1212,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570647</v>
+        <v>570595</v>
       </c>
       <c r="R7" t="n">
-        <v>6684973</v>
+        <v>6685327</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 3942-2025 artfynd.xlsx
+++ b/artfynd/A 3942-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122837225</v>
+        <v>122837234</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>80723</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570644</v>
+        <v>570628</v>
       </c>
       <c r="R3" t="n">
-        <v>6685226</v>
+        <v>6685273</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122837234</v>
+        <v>122837236</v>
       </c>
       <c r="B6" t="n">
-        <v>80723</v>
+        <v>92225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570628</v>
+        <v>570595</v>
       </c>
       <c r="R6" t="n">
-        <v>6685273</v>
+        <v>6685327</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122837236</v>
+        <v>122837225</v>
       </c>
       <c r="B7" t="n">
-        <v>92225</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,38 +1207,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570595</v>
+        <v>570644</v>
       </c>
       <c r="R7" t="n">
-        <v>6685327</v>
+        <v>6685226</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 3942-2025 artfynd.xlsx
+++ b/artfynd/A 3942-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122837226</v>
+        <v>122837234</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>80723</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570647</v>
+        <v>570628</v>
       </c>
       <c r="R2" t="n">
-        <v>6684973</v>
+        <v>6685273</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122837234</v>
+        <v>122837236</v>
       </c>
       <c r="B3" t="n">
-        <v>80723</v>
+        <v>92233</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570628</v>
+        <v>570595</v>
       </c>
       <c r="R3" t="n">
-        <v>6685273</v>
+        <v>6685327</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122837222</v>
+        <v>122837223</v>
       </c>
       <c r="B4" t="n">
-        <v>5193</v>
+        <v>90917</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,39 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570597</v>
+        <v>570628</v>
       </c>
       <c r="R4" t="n">
-        <v>6685181</v>
+        <v>6685316</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837223</v>
+        <v>122837226</v>
       </c>
       <c r="B5" t="n">
-        <v>90909</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,38 +993,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570628</v>
+        <v>570647</v>
       </c>
       <c r="R5" t="n">
-        <v>6685316</v>
+        <v>6684973</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122837236</v>
+        <v>122837222</v>
       </c>
       <c r="B6" t="n">
-        <v>92225</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,34 +1104,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570595</v>
+        <v>570597</v>
       </c>
       <c r="R6" t="n">
-        <v>6685327</v>
+        <v>6685181</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 3942-2025 artfynd.xlsx
+++ b/artfynd/A 3942-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122837234</v>
+        <v>122837236</v>
       </c>
       <c r="B2" t="n">
-        <v>80723</v>
+        <v>92233</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570628</v>
+        <v>570595</v>
       </c>
       <c r="R2" t="n">
-        <v>6685273</v>
+        <v>6685327</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122837236</v>
+        <v>122837225</v>
       </c>
       <c r="B3" t="n">
-        <v>92233</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570595</v>
+        <v>570644</v>
       </c>
       <c r="R3" t="n">
-        <v>6685327</v>
+        <v>6685226</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122837223</v>
+        <v>122837234</v>
       </c>
       <c r="B4" t="n">
-        <v>90917</v>
+        <v>80723</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,7 +927,7 @@
         <v>570628</v>
       </c>
       <c r="R4" t="n">
-        <v>6685316</v>
+        <v>6685273</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837226</v>
+        <v>122837222</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>5193</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,20 +998,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1017,7 +1022,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570647</v>
+        <v>570597</v>
       </c>
       <c r="R5" t="n">
-        <v>6684973</v>
+        <v>6685181</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122837222</v>
+        <v>122837226</v>
       </c>
       <c r="B6" t="n">
-        <v>5193</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,20 +1105,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1124,7 +1129,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570597</v>
+        <v>570647</v>
       </c>
       <c r="R6" t="n">
-        <v>6685181</v>
+        <v>6684973</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122837225</v>
+        <v>122837223</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>90917</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,43 +1212,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570644</v>
+        <v>570628</v>
       </c>
       <c r="R7" t="n">
-        <v>6685226</v>
+        <v>6685316</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 3942-2025 artfynd.xlsx
+++ b/artfynd/A 3942-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122837236</v>
+        <v>122837222</v>
       </c>
       <c r="B2" t="n">
-        <v>92233</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570595</v>
+        <v>570597</v>
       </c>
       <c r="R2" t="n">
-        <v>6685327</v>
+        <v>6685181</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122837225</v>
+        <v>122837236</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>92233</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,43 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570644</v>
+        <v>570595</v>
       </c>
       <c r="R3" t="n">
-        <v>6685226</v>
+        <v>6685327</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837222</v>
+        <v>122837225</v>
       </c>
       <c r="B5" t="n">
-        <v>5193</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,20 +998,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1022,7 +1022,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570597</v>
+        <v>570644</v>
       </c>
       <c r="R5" t="n">
-        <v>6685181</v>
+        <v>6685226</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 3942-2025 artfynd.xlsx
+++ b/artfynd/A 3942-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122837222</v>
+        <v>122837234</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>80723</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570597</v>
+        <v>570628</v>
       </c>
       <c r="R2" t="n">
-        <v>6685181</v>
+        <v>6685273</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122837236</v>
+        <v>122837223</v>
       </c>
       <c r="B3" t="n">
-        <v>92233</v>
+        <v>90917</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570595</v>
+        <v>570628</v>
       </c>
       <c r="R3" t="n">
-        <v>6685327</v>
+        <v>6685316</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122837234</v>
+        <v>122837225</v>
       </c>
       <c r="B4" t="n">
-        <v>80723</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570628</v>
+        <v>570644</v>
       </c>
       <c r="R4" t="n">
-        <v>6685273</v>
+        <v>6685226</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837225</v>
+        <v>122837222</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>5193</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,20 +998,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1022,7 +1022,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570644</v>
+        <v>570597</v>
       </c>
       <c r="R5" t="n">
-        <v>6685226</v>
+        <v>6685181</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122837226</v>
+        <v>122837236</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>92233</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,43 +1105,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570647</v>
+        <v>570595</v>
       </c>
       <c r="R6" t="n">
-        <v>6684973</v>
+        <v>6685327</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122837223</v>
+        <v>122837226</v>
       </c>
       <c r="B7" t="n">
-        <v>90917</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,38 +1207,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570628</v>
+        <v>570647</v>
       </c>
       <c r="R7" t="n">
-        <v>6685316</v>
+        <v>6684973</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 3942-2025 artfynd.xlsx
+++ b/artfynd/A 3942-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122837234</v>
+        <v>122837225</v>
       </c>
       <c r="B2" t="n">
-        <v>80723</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570628</v>
+        <v>570644</v>
       </c>
       <c r="R2" t="n">
-        <v>6685273</v>
+        <v>6685226</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +785,7 @@
         <v>122837223</v>
       </c>
       <c r="B3" t="n">
-        <v>90917</v>
+        <v>90920</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122837225</v>
+        <v>122837222</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>5193</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,20 +896,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -915,7 +920,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570644</v>
+        <v>570597</v>
       </c>
       <c r="R4" t="n">
-        <v>6685226</v>
+        <v>6685181</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837222</v>
+        <v>122837234</v>
       </c>
       <c r="B5" t="n">
-        <v>5193</v>
+        <v>80726</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,43 +1003,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570597</v>
+        <v>570628</v>
       </c>
       <c r="R5" t="n">
-        <v>6685181</v>
+        <v>6685273</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
         <v>122837236</v>
       </c>
       <c r="B6" t="n">
-        <v>92233</v>
+        <v>92236</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>122837226</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 3942-2025 artfynd.xlsx
+++ b/artfynd/A 3942-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122837225</v>
+        <v>122837226</v>
       </c>
       <c r="B2" t="n">
         <v>57497</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570644</v>
+        <v>570647</v>
       </c>
       <c r="R2" t="n">
-        <v>6685226</v>
+        <v>6684973</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122837223</v>
+        <v>122837234</v>
       </c>
       <c r="B3" t="n">
-        <v>90920</v>
+        <v>80728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,7 +825,7 @@
         <v>570628</v>
       </c>
       <c r="R3" t="n">
-        <v>6685316</v>
+        <v>6685273</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122837222</v>
+        <v>122837236</v>
       </c>
       <c r="B4" t="n">
-        <v>5193</v>
+        <v>92238</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570597</v>
+        <v>570595</v>
       </c>
       <c r="R4" t="n">
-        <v>6685181</v>
+        <v>6685327</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837234</v>
+        <v>122837222</v>
       </c>
       <c r="B5" t="n">
-        <v>80726</v>
+        <v>5193</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,38 +998,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570628</v>
+        <v>570597</v>
       </c>
       <c r="R5" t="n">
-        <v>6685273</v>
+        <v>6685181</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122837236</v>
+        <v>122837223</v>
       </c>
       <c r="B6" t="n">
-        <v>92236</v>
+        <v>90922</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570595</v>
+        <v>570628</v>
       </c>
       <c r="R6" t="n">
-        <v>6685327</v>
+        <v>6685316</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122837226</v>
+        <v>122837225</v>
       </c>
       <c r="B7" t="n">
         <v>57497</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570647</v>
+        <v>570644</v>
       </c>
       <c r="R7" t="n">
-        <v>6684973</v>
+        <v>6685226</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 3942-2025 artfynd.xlsx
+++ b/artfynd/A 3942-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122837226</v>
+        <v>122837225</v>
       </c>
       <c r="B2" t="n">
         <v>57497</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570647</v>
+        <v>570644</v>
       </c>
       <c r="R2" t="n">
-        <v>6684973</v>
+        <v>6685226</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122837234</v>
+        <v>122837222</v>
       </c>
       <c r="B3" t="n">
-        <v>80728</v>
+        <v>5193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +794,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1049</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570628</v>
+        <v>570597</v>
       </c>
       <c r="R3" t="n">
-        <v>6685273</v>
+        <v>6685181</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122837236</v>
+        <v>122837226</v>
       </c>
       <c r="B4" t="n">
-        <v>92238</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,38 +901,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570595</v>
+        <v>570647</v>
       </c>
       <c r="R4" t="n">
-        <v>6685327</v>
+        <v>6684973</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122837222</v>
+        <v>122837234</v>
       </c>
       <c r="B5" t="n">
-        <v>5193</v>
+        <v>80729</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,43 +1008,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570597</v>
+        <v>570628</v>
       </c>
       <c r="R5" t="n">
-        <v>6685181</v>
+        <v>6685273</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1101,7 @@
         <v>122837223</v>
       </c>
       <c r="B6" t="n">
-        <v>90922</v>
+        <v>90928</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122837225</v>
+        <v>122837236</v>
       </c>
       <c r="B7" t="n">
-        <v>57497</v>
+        <v>92244</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,43 +1212,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ljusfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570644</v>
+        <v>570595</v>
       </c>
       <c r="R7" t="n">
-        <v>6685226</v>
+        <v>6685327</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
